--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H496"/>
+  <dimension ref="A1:H498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15314,6 +15314,66 @@
       <c r="H496" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:01:21+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>314.91</v>
+      </c>
+      <c r="C497" t="n">
+        <v>323.47</v>
+      </c>
+      <c r="D497" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="E497" t="n">
+        <v>331.81</v>
+      </c>
+      <c r="F497" t="n">
+        <v>330.11</v>
+      </c>
+      <c r="G497" t="n">
+        <v>331.79</v>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>313.92</v>
+      </c>
+      <c r="C498" t="n">
+        <v>322.84</v>
+      </c>
+      <c r="D498" t="n">
+        <v>329.18</v>
+      </c>
+      <c r="E498" t="n">
+        <v>331.58</v>
+      </c>
+      <c r="F498" t="n">
+        <v>329.49</v>
+      </c>
+      <c r="G498" t="n">
+        <v>331.76</v>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -15328,7 +15388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20611,6 +20671,36 @@
       </c>
       <c r="B528" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2025-12-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -20779,28 +20869,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.58490108378404</v>
+        <v>-2.587857722912662</v>
       </c>
       <c r="J2" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K2" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8879212732259616</v>
+        <v>0.888796594737248</v>
       </c>
       <c r="M2" t="n">
-        <v>5.42315633791976</v>
+        <v>5.415095938525553</v>
       </c>
       <c r="N2" t="n">
-        <v>48.74692511842856</v>
+        <v>48.61574578326449</v>
       </c>
       <c r="O2" t="n">
-        <v>6.981899821569238</v>
+        <v>6.972499249427316</v>
       </c>
       <c r="P2" t="n">
-        <v>386.5124206332573</v>
+        <v>386.5427499502514</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20857,28 +20947,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.418331824918886</v>
+        <v>-2.416930448402903</v>
       </c>
       <c r="J3" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K3" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L3" t="n">
-        <v>0.914077059650826</v>
+        <v>0.9145668123285426</v>
       </c>
       <c r="M3" t="n">
-        <v>4.430137379121249</v>
+        <v>4.420304076900337</v>
       </c>
       <c r="N3" t="n">
-        <v>31.77376978714741</v>
+        <v>31.66065795001283</v>
       </c>
       <c r="O3" t="n">
-        <v>5.636822667704512</v>
+        <v>5.626780424897779</v>
       </c>
       <c r="P3" t="n">
-        <v>384.9489822865932</v>
+        <v>384.934609028111</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20935,28 +21025,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.21839531095208</v>
+        <v>-2.217366985165148</v>
       </c>
       <c r="J4" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K4" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9178241543195909</v>
+        <v>0.9183228886789611</v>
       </c>
       <c r="M4" t="n">
-        <v>3.692694321685991</v>
+        <v>3.684148789182435</v>
       </c>
       <c r="N4" t="n">
-        <v>25.46673199903483</v>
+        <v>25.37234284098097</v>
       </c>
       <c r="O4" t="n">
-        <v>5.046457371169881</v>
+        <v>5.037096667821749</v>
       </c>
       <c r="P4" t="n">
-        <v>386.5209051612829</v>
+        <v>386.5103584167974</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21013,28 +21103,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.151733183257712</v>
+        <v>-2.151216755863255</v>
       </c>
       <c r="J5" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K5" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9323414089900349</v>
+        <v>0.9328000926066141</v>
       </c>
       <c r="M5" t="n">
-        <v>3.160598687235793</v>
+        <v>3.150583493481563</v>
       </c>
       <c r="N5" t="n">
-        <v>19.41938412268827</v>
+        <v>19.34322548980063</v>
       </c>
       <c r="O5" t="n">
-        <v>4.406743028892004</v>
+        <v>4.398093392573721</v>
       </c>
       <c r="P5" t="n">
-        <v>387.6664422170044</v>
+        <v>387.6611453834645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21091,28 +21181,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.114818334160812</v>
+        <v>-2.114544403653295</v>
       </c>
       <c r="J6" t="n">
+        <v>497</v>
+      </c>
+      <c r="K6" t="n">
         <v>495</v>
       </c>
-      <c r="K6" t="n">
-        <v>493</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.9315601642339829</v>
+        <v>0.932043985825554</v>
       </c>
       <c r="M6" t="n">
-        <v>3.204527670582741</v>
+        <v>3.193390171924317</v>
       </c>
       <c r="N6" t="n">
-        <v>18.73972430435794</v>
+        <v>18.66488456798086</v>
       </c>
       <c r="O6" t="n">
-        <v>4.328940321182303</v>
+        <v>4.320287556168092</v>
       </c>
       <c r="P6" t="n">
-        <v>385.1294713545026</v>
+        <v>385.1266344540662</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21169,28 +21259,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.910256623233657</v>
+        <v>-1.909737827016486</v>
       </c>
       <c r="J7" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K7" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9289865655716134</v>
+        <v>0.9294602886836353</v>
       </c>
       <c r="M7" t="n">
-        <v>2.843575068717867</v>
+        <v>2.83537603444846</v>
       </c>
       <c r="N7" t="n">
-        <v>16.14475278108472</v>
+        <v>16.08163264723284</v>
       </c>
       <c r="O7" t="n">
-        <v>4.01805335717244</v>
+        <v>4.01019109859279</v>
       </c>
       <c r="P7" t="n">
-        <v>381.3827752560714</v>
+        <v>381.377455476218</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21228,7 +21318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H496"/>
+  <dimension ref="A1:H498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42051,6 +42141,90 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:01:21+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-41.15352472011657,176.02769480158662</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-41.15387962216732,176.0269259129505</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-41.1542165379068,176.026145234113</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-41.154518610731955,176.02534171589244</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-41.154790760133025,176.02451858368158</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-41.15509016902331,176.02371332067634</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-41.15351673556656,176.02768956757234</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-41.153874541074444,176.0269225822317</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-41.15421153745037,176.02614195628195</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-41.15451675571779,176.0253404999313</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-41.15478575964272,176.0245153058994</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-41.15508992706329,176.02371316207507</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H498"/>
+  <dimension ref="A1:H499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15374,6 +15374,36 @@
       <c r="H498" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:55:07+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>314.26</v>
+      </c>
+      <c r="C499" t="n">
+        <v>324.42</v>
+      </c>
+      <c r="D499" t="n">
+        <v>328.88</v>
+      </c>
+      <c r="E499" t="n">
+        <v>331.13</v>
+      </c>
+      <c r="F499" t="n">
+        <v>329.11</v>
+      </c>
+      <c r="G499" t="n">
+        <v>331.61</v>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15388,7 +15418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20701,6 +20731,16 @@
       </c>
       <c r="B531" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-02-04 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -20869,28 +20909,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.587857722912662</v>
+        <v>-2.58924715425738</v>
       </c>
       <c r="J2" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K2" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.888796594737248</v>
+        <v>0.8892401092170831</v>
       </c>
       <c r="M2" t="n">
-        <v>5.415095938525553</v>
+        <v>5.410582414170401</v>
       </c>
       <c r="N2" t="n">
-        <v>48.61574578326449</v>
+        <v>48.54613421541968</v>
       </c>
       <c r="O2" t="n">
-        <v>6.972499249427316</v>
+        <v>6.967505594932786</v>
       </c>
       <c r="P2" t="n">
-        <v>386.5427499502514</v>
+        <v>386.5571043066698</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20947,28 +20987,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.416930448402903</v>
+        <v>-2.415634025295012</v>
       </c>
       <c r="J3" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K3" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9145668123285426</v>
+        <v>0.914734983256932</v>
       </c>
       <c r="M3" t="n">
-        <v>4.420304076900337</v>
+        <v>4.418715431414367</v>
       </c>
       <c r="N3" t="n">
-        <v>31.66065795001283</v>
+        <v>31.62146823419141</v>
       </c>
       <c r="O3" t="n">
-        <v>5.626780424897779</v>
+        <v>5.623296918551555</v>
       </c>
       <c r="P3" t="n">
-        <v>384.934609028111</v>
+        <v>384.9212155492389</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21025,28 +21065,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.217366985165148</v>
+        <v>-2.216961033739588</v>
       </c>
       <c r="J4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9183228886789611</v>
+        <v>0.9185878815735748</v>
       </c>
       <c r="M4" t="n">
-        <v>3.684148789182435</v>
+        <v>3.679209855953089</v>
       </c>
       <c r="N4" t="n">
-        <v>25.37234284098097</v>
+        <v>25.3237854377575</v>
       </c>
       <c r="O4" t="n">
-        <v>5.037096667821749</v>
+        <v>5.032274380213931</v>
       </c>
       <c r="P4" t="n">
-        <v>386.5103584167974</v>
+        <v>386.5061644913665</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21103,28 +21143,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.151216755863255</v>
+        <v>-2.151053213326882</v>
       </c>
       <c r="J5" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K5" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9328000926066141</v>
+        <v>0.9330395657659378</v>
       </c>
       <c r="M5" t="n">
-        <v>3.150583493481563</v>
+        <v>3.145098890460156</v>
       </c>
       <c r="N5" t="n">
-        <v>19.34322548980063</v>
+        <v>19.3047717385942</v>
       </c>
       <c r="O5" t="n">
-        <v>4.398093392573721</v>
+        <v>4.393719578966573</v>
       </c>
       <c r="P5" t="n">
-        <v>387.6611453834645</v>
+        <v>387.6594558089017</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21181,28 +21221,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.114544403653295</v>
+        <v>-2.114551679534833</v>
       </c>
       <c r="J6" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K6" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.932043985825554</v>
+        <v>0.9322986455890137</v>
       </c>
       <c r="M6" t="n">
-        <v>3.193390171924317</v>
+        <v>3.186982264497578</v>
       </c>
       <c r="N6" t="n">
-        <v>18.66488456798086</v>
+        <v>18.62725450611661</v>
       </c>
       <c r="O6" t="n">
-        <v>4.320287556168092</v>
+        <v>4.315930317569621</v>
       </c>
       <c r="P6" t="n">
-        <v>385.1266344540662</v>
+        <v>385.1267103727885</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21259,28 +21299,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.909737827016486</v>
+        <v>-1.909436291342937</v>
       </c>
       <c r="J7" t="n">
+        <v>498</v>
+      </c>
+      <c r="K7" t="n">
         <v>497</v>
       </c>
-      <c r="K7" t="n">
-        <v>496</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.9294602886836353</v>
+        <v>0.9296957402484659</v>
       </c>
       <c r="M7" t="n">
-        <v>2.83537603444846</v>
+        <v>2.831542599689823</v>
       </c>
       <c r="N7" t="n">
-        <v>16.08163264723284</v>
+        <v>16.0505975691146</v>
       </c>
       <c r="O7" t="n">
-        <v>4.01019109859279</v>
+        <v>4.006319703807298</v>
       </c>
       <c r="P7" t="n">
-        <v>381.377455476218</v>
+        <v>381.3743412335811</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21318,7 +21358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H498"/>
+  <dimension ref="A1:H499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42225,6 +42265,48 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:55:07+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-41.153519477735294,176.02769136511245</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-41.15388728413255,176.02693093546404</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-41.154209117874636,176.02614037023488</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-41.15451312634219,176.02533812087708</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-41.15478269482603,176.02451329693636</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-41.15508871726323,176.02371236906882</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H499"/>
+  <dimension ref="A1:H503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15402,6 +15402,126 @@
         <v>331.61</v>
       </c>
       <c r="H499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:40+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>315.28</v>
+      </c>
+      <c r="C500" t="n">
+        <v>326.29</v>
+      </c>
+      <c r="D500" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="E500" t="n">
+        <v>332.42</v>
+      </c>
+      <c r="F500" t="n">
+        <v>329.91</v>
+      </c>
+      <c r="G500" t="n">
+        <v>332.08</v>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:50+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>318.12</v>
+      </c>
+      <c r="C501" t="n">
+        <v>328.11</v>
+      </c>
+      <c r="D501" t="n">
+        <v>331.37</v>
+      </c>
+      <c r="E501" t="n">
+        <v>332.66</v>
+      </c>
+      <c r="F501" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="G501" t="n">
+        <v>331.91</v>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>318.77</v>
+      </c>
+      <c r="C502" t="n">
+        <v>328.53</v>
+      </c>
+      <c r="D502" t="n">
+        <v>331.48</v>
+      </c>
+      <c r="E502" t="n">
+        <v>333</v>
+      </c>
+      <c r="F502" t="n">
+        <v>330.51</v>
+      </c>
+      <c r="G502" t="n">
+        <v>332.08</v>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:01:01+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>319.24</v>
+      </c>
+      <c r="C503" t="n">
+        <v>329.09</v>
+      </c>
+      <c r="D503" t="n">
+        <v>331.89</v>
+      </c>
+      <c r="E503" t="n">
+        <v>333.05</v>
+      </c>
+      <c r="F503" t="n">
+        <v>330.18</v>
+      </c>
+      <c r="G503" t="n">
+        <v>332.24</v>
+      </c>
+      <c r="H503" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15418,7 +15538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B532"/>
+  <dimension ref="A1:B536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20741,6 +20861,46 @@
       </c>
       <c r="B532" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -20909,28 +21069,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.58924715425738</v>
+        <v>-2.589155197898255</v>
       </c>
       <c r="J2" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K2" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8892401092170831</v>
+        <v>0.8907483527783645</v>
       </c>
       <c r="M2" t="n">
-        <v>5.410582414170401</v>
+        <v>5.378368642079185</v>
       </c>
       <c r="N2" t="n">
-        <v>48.54613421541968</v>
+        <v>48.17960133582267</v>
       </c>
       <c r="O2" t="n">
-        <v>6.967505594932786</v>
+        <v>6.941152738257721</v>
       </c>
       <c r="P2" t="n">
-        <v>386.5571043066698</v>
+        <v>386.5561241448119</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20987,28 +21147,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.415634025295012</v>
+        <v>-2.405071461542253</v>
       </c>
       <c r="J3" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K3" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L3" t="n">
-        <v>0.914734983256932</v>
+        <v>0.9142591298806709</v>
       </c>
       <c r="M3" t="n">
-        <v>4.418715431414367</v>
+        <v>4.443129030131034</v>
       </c>
       <c r="N3" t="n">
-        <v>31.62146823419141</v>
+        <v>31.78693252138428</v>
       </c>
       <c r="O3" t="n">
-        <v>5.623296918551555</v>
+        <v>5.637990113629527</v>
       </c>
       <c r="P3" t="n">
-        <v>384.9212155492389</v>
+        <v>384.8116790178596</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21065,28 +21225,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.216961033739588</v>
+        <v>-2.211709772328885</v>
       </c>
       <c r="J4" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K4" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9185878815735748</v>
+        <v>0.9191099349140981</v>
       </c>
       <c r="M4" t="n">
-        <v>3.679209855953089</v>
+        <v>3.681927023822687</v>
       </c>
       <c r="N4" t="n">
-        <v>25.3237854377575</v>
+        <v>25.22656203457325</v>
       </c>
       <c r="O4" t="n">
-        <v>5.032274380213931</v>
+        <v>5.022605104382909</v>
       </c>
       <c r="P4" t="n">
-        <v>386.5061644913665</v>
+        <v>386.4517052662758</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21143,28 +21303,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.151053213326882</v>
+        <v>-2.147767027448695</v>
       </c>
       <c r="J5" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K5" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9330395657659378</v>
+        <v>0.9337076030953093</v>
       </c>
       <c r="M5" t="n">
-        <v>3.145098890460156</v>
+        <v>3.13676567020435</v>
       </c>
       <c r="N5" t="n">
-        <v>19.3047717385942</v>
+        <v>19.19116050108097</v>
       </c>
       <c r="O5" t="n">
-        <v>4.393719578966573</v>
+        <v>4.380771678720653</v>
       </c>
       <c r="P5" t="n">
-        <v>387.6594558089017</v>
+        <v>387.6253777652089</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21221,28 +21381,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.114551679534833</v>
+        <v>-2.112697829726375</v>
       </c>
       <c r="J6" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K6" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9322986455890137</v>
+        <v>0.9331480905520152</v>
       </c>
       <c r="M6" t="n">
-        <v>3.186982264497578</v>
+        <v>3.173494849438566</v>
       </c>
       <c r="N6" t="n">
-        <v>18.62725450611661</v>
+        <v>18.49106005646718</v>
       </c>
       <c r="O6" t="n">
-        <v>4.315930317569621</v>
+        <v>4.300123260613256</v>
       </c>
       <c r="P6" t="n">
-        <v>385.1267103727885</v>
+        <v>385.1072944973172</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21299,28 +21459,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.909436291342937</v>
+        <v>-1.907373103263053</v>
       </c>
       <c r="J7" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K7" t="n">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9296957402484659</v>
+        <v>0.9305232513086212</v>
       </c>
       <c r="M7" t="n">
-        <v>2.831542599689823</v>
+        <v>2.821646183526795</v>
       </c>
       <c r="N7" t="n">
-        <v>16.0505975691146</v>
+        <v>15.93822261019791</v>
       </c>
       <c r="O7" t="n">
-        <v>4.006319703807298</v>
+        <v>3.992270357853775</v>
       </c>
       <c r="P7" t="n">
-        <v>381.3743412335811</v>
+        <v>381.3529533446622</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21358,7 +21518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H499"/>
+  <dimension ref="A1:H503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42307,6 +42467,174 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:40+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-41.15352770424124,176.0276967577337</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-41.15390236610543,176.02694082188896</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-41.154219522050084,176.0261471902382</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-41.154523530552076,176.0253449408332</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-41.15478914707165,176.02451752633243</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-41.15509250797007,176.02371485382187</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:50+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-41.15355060941303,176.02771177249048</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-41.15391704481599,176.02695044397547</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-41.15422920035236,176.0261535344293</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-41.15452546621897,176.02534620966253</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-41.15479229254132,176.02451958816334</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-41.15509113686335,176.02371395508138</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-41.15355585179356,176.027715208968</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-41.15392043221061,176.02695266445755</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-41.154230087530046,176.02615411598026</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-41.154528208413716,176.02534800717083</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-41.15479398625575,176.02452069838003</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-41.15509250797007,176.02371485382187</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:01:01+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-41.15355964243787,176.02771769380595</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-41.15392494873666,176.02695562510078</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-41.15423339428322,176.02615628357938</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-41.15452861167765,176.0253482715103</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-41.15479132470451,176.02451895375378</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-41.15509379842345,176.02371569969534</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H503"/>
+  <dimension ref="A1:H506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15522,6 +15522,96 @@
         <v>332.24</v>
       </c>
       <c r="H503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>320.08</v>
+      </c>
+      <c r="C504" t="n">
+        <v>329.62</v>
+      </c>
+      <c r="D504" t="n">
+        <v>332.89</v>
+      </c>
+      <c r="E504" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="F504" t="n">
+        <v>330.38</v>
+      </c>
+      <c r="G504" t="n">
+        <v>333.03</v>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:38+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>319.71</v>
+      </c>
+      <c r="C505" t="n">
+        <v>328.82</v>
+      </c>
+      <c r="D505" t="n">
+        <v>333.05</v>
+      </c>
+      <c r="E505" t="n">
+        <v>333.49</v>
+      </c>
+      <c r="F505" t="n">
+        <v>330.07</v>
+      </c>
+      <c r="G505" t="n">
+        <v>332.47</v>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:36+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="C506" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="D506" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="E506" t="n">
+        <v>334.12</v>
+      </c>
+      <c r="F506" t="n">
+        <v>330.7</v>
+      </c>
+      <c r="G506" t="n">
+        <v>332.72</v>
+      </c>
+      <c r="H506" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15538,7 +15628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B536"/>
+  <dimension ref="A1:B539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20901,6 +20991,36 @@
       </c>
       <c r="B536" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -21069,28 +21189,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.589155197898255</v>
+        <v>-2.58714440884264</v>
       </c>
       <c r="J2" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8907483527783645</v>
+        <v>0.8916972436841296</v>
       </c>
       <c r="M2" t="n">
-        <v>5.378368642079185</v>
+        <v>5.358783708477449</v>
       </c>
       <c r="N2" t="n">
-        <v>48.17960133582267</v>
+        <v>47.91585716200539</v>
       </c>
       <c r="O2" t="n">
-        <v>6.941152738257721</v>
+        <v>6.922128080439237</v>
       </c>
       <c r="P2" t="n">
-        <v>386.5561241448119</v>
+        <v>386.5351872607367</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21147,28 +21267,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.405071461542253</v>
+        <v>-2.396130826563112</v>
       </c>
       <c r="J3" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9142591298806709</v>
+        <v>0.9136183432666802</v>
       </c>
       <c r="M3" t="n">
-        <v>4.443129030131034</v>
+        <v>4.466940208883952</v>
       </c>
       <c r="N3" t="n">
-        <v>31.78693252138428</v>
+        <v>31.99584661708961</v>
       </c>
       <c r="O3" t="n">
-        <v>5.637990113629527</v>
+        <v>5.656487126926889</v>
       </c>
       <c r="P3" t="n">
-        <v>384.8116790178596</v>
+        <v>384.7185410722937</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21225,28 +21345,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.211709772328885</v>
+        <v>-2.205755811107717</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K4" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9191099349140981</v>
+        <v>0.9190673857125174</v>
       </c>
       <c r="M4" t="n">
-        <v>3.681927023822687</v>
+        <v>3.695994444492543</v>
       </c>
       <c r="N4" t="n">
-        <v>25.22656203457325</v>
+        <v>25.25264730254823</v>
       </c>
       <c r="O4" t="n">
-        <v>5.022605104382909</v>
+        <v>5.025201220105343</v>
       </c>
       <c r="P4" t="n">
-        <v>386.4517052662758</v>
+        <v>386.3896724966909</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21303,28 +21423,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.147767027448695</v>
+        <v>-2.144143826796187</v>
       </c>
       <c r="J5" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K5" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9337076030953093</v>
+        <v>0.9340156807253575</v>
       </c>
       <c r="M5" t="n">
-        <v>3.13676567020435</v>
+        <v>3.136401631226486</v>
       </c>
       <c r="N5" t="n">
-        <v>19.19116050108097</v>
+        <v>19.14301042496759</v>
       </c>
       <c r="O5" t="n">
-        <v>4.380771678720653</v>
+        <v>4.375272611502921</v>
       </c>
       <c r="P5" t="n">
-        <v>387.6253777652089</v>
+        <v>387.5876234893997</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21381,28 +21501,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.112697829726375</v>
+        <v>-2.110950009892586</v>
       </c>
       <c r="J6" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9331480905520152</v>
+        <v>0.933730972547624</v>
       </c>
       <c r="M6" t="n">
-        <v>3.173494849438566</v>
+        <v>3.165755537883515</v>
       </c>
       <c r="N6" t="n">
-        <v>18.49106005646718</v>
+        <v>18.39619501334948</v>
       </c>
       <c r="O6" t="n">
-        <v>4.300123260613256</v>
+        <v>4.289078573930476</v>
       </c>
       <c r="P6" t="n">
-        <v>385.1072944973172</v>
+        <v>385.0889006574184</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21459,28 +21579,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.907373103263053</v>
+        <v>-1.904953947820547</v>
       </c>
       <c r="J7" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K7" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9305232513086212</v>
+        <v>0.9310008543259608</v>
       </c>
       <c r="M7" t="n">
-        <v>2.821646183526795</v>
+        <v>2.819652280414239</v>
       </c>
       <c r="N7" t="n">
-        <v>15.93822261019791</v>
+        <v>15.87269134261775</v>
       </c>
       <c r="O7" t="n">
-        <v>3.992270357853775</v>
+        <v>3.984054635998074</v>
       </c>
       <c r="P7" t="n">
-        <v>381.3529533446622</v>
+        <v>381.3277578661628</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21518,7 +21638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H503"/>
+  <dimension ref="A1:H506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42635,6 +42755,132 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-41.15356641720624,176.02772213479372</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-41.15392922330589,176.02695842713848</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-41.15424145953464,176.0261615704075</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-41.15453240235857,176.0253507563015</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-41.154792937765855,176.02452001110302</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-41.155100170036896,176.023719876196</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:38+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-41.15356343308209,176.02772017864424</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-41.1539227711259,176.02695419764774</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-41.15424274997483,176.02616241630014</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-41.15453216040021,176.02535059769778</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-41.15479043752075,176.02451837221173</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-41.15509565345018,176.02371691563846</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:36+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-41.15355286766927,176.02771325281918</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-41.15391938373133,176.02695197716545</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-41.154242427364785,176.02616220482696</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-41.154537241525574,176.02535392837572</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-41.15479551866402,176.0245217028619</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-41.15509766978355,176.02371823731588</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H506"/>
+  <dimension ref="A1:H511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15612,6 +15612,156 @@
         <v>332.72</v>
       </c>
       <c r="H506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>319.63</v>
+      </c>
+      <c r="C507" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="D507" t="n">
+        <v>332.68</v>
+      </c>
+      <c r="E507" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="F507" t="n">
+        <v>331.35</v>
+      </c>
+      <c r="G507" t="n">
+        <v>332.43</v>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:54:16+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>319.98</v>
+      </c>
+      <c r="C508" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="D508" t="n">
+        <v>332.43</v>
+      </c>
+      <c r="E508" t="n">
+        <v>335.65</v>
+      </c>
+      <c r="F508" t="n">
+        <v>331.88</v>
+      </c>
+      <c r="G508" t="n">
+        <v>332.43</v>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>321.72</v>
+      </c>
+      <c r="C509" t="n">
+        <v>330.04</v>
+      </c>
+      <c r="D509" t="n">
+        <v>332.63</v>
+      </c>
+      <c r="E509" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="F509" t="n">
+        <v>332.29</v>
+      </c>
+      <c r="G509" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="C510" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="D510" t="n">
+        <v>332.35</v>
+      </c>
+      <c r="E510" t="n">
+        <v>335.56</v>
+      </c>
+      <c r="F510" t="n">
+        <v>332.02</v>
+      </c>
+      <c r="G510" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>321.1</v>
+      </c>
+      <c r="C511" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="D511" t="n">
+        <v>332.27</v>
+      </c>
+      <c r="E511" t="n">
+        <v>335.39</v>
+      </c>
+      <c r="F511" t="n">
+        <v>331.74</v>
+      </c>
+      <c r="G511" t="n">
+        <v>332.13</v>
+      </c>
+      <c r="H511" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15628,7 +15778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B539"/>
+  <dimension ref="A1:B544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21021,6 +21171,56 @@
       </c>
       <c r="B539" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -21189,28 +21389,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.58714440884264</v>
+        <v>-2.581178051378834</v>
       </c>
       <c r="J2" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="K2" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8916972436841296</v>
+        <v>0.8928830388774621</v>
       </c>
       <c r="M2" t="n">
-        <v>5.358783708477449</v>
+        <v>5.342466970941737</v>
       </c>
       <c r="N2" t="n">
-        <v>47.91585716200539</v>
+        <v>47.5609103671654</v>
       </c>
       <c r="O2" t="n">
-        <v>6.922128080439237</v>
+        <v>6.896441862813417</v>
       </c>
       <c r="P2" t="n">
-        <v>386.5351872607367</v>
+        <v>386.4727672370725</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21267,28 +21467,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.396130826563112</v>
+        <v>-2.380283144312241</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9136183432666802</v>
+        <v>0.912206003152494</v>
       </c>
       <c r="M3" t="n">
-        <v>4.466940208883952</v>
+        <v>4.514850240789157</v>
       </c>
       <c r="N3" t="n">
-        <v>31.99584661708961</v>
+        <v>32.44738478989174</v>
       </c>
       <c r="O3" t="n">
-        <v>5.656487126926889</v>
+        <v>5.696260597083997</v>
       </c>
       <c r="P3" t="n">
-        <v>384.7185410722937</v>
+        <v>384.5527632317396</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21345,28 +21545,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.205755811107717</v>
+        <v>-2.196794977973306</v>
       </c>
       <c r="J4" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="K4" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9190673857125174</v>
+        <v>0.9191791138529414</v>
       </c>
       <c r="M4" t="n">
-        <v>3.695994444492543</v>
+        <v>3.713990667848423</v>
       </c>
       <c r="N4" t="n">
-        <v>25.25264730254823</v>
+        <v>25.24951708105859</v>
       </c>
       <c r="O4" t="n">
-        <v>5.025201220105343</v>
+        <v>5.024889758100031</v>
       </c>
       <c r="P4" t="n">
-        <v>386.3896724966909</v>
+        <v>386.2959393006879</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21423,28 +21623,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.144143826796187</v>
+        <v>-2.134960832914614</v>
       </c>
       <c r="J5" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="K5" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9340156807253575</v>
+        <v>0.9338491609014723</v>
       </c>
       <c r="M5" t="n">
-        <v>3.136401631226486</v>
+        <v>3.152992926131599</v>
       </c>
       <c r="N5" t="n">
-        <v>19.14301042496759</v>
+        <v>19.21272693887974</v>
       </c>
       <c r="O5" t="n">
-        <v>4.375272611502921</v>
+        <v>4.383232476024941</v>
       </c>
       <c r="P5" t="n">
-        <v>387.5876234893997</v>
+        <v>387.4915636002148</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21501,28 +21701,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.110950009892586</v>
+        <v>-2.105202404413347</v>
       </c>
       <c r="J6" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="K6" t="n">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="L6" t="n">
-        <v>0.933730972547624</v>
+        <v>0.9342591969266896</v>
       </c>
       <c r="M6" t="n">
-        <v>3.165755537883515</v>
+        <v>3.171461873754909</v>
       </c>
       <c r="N6" t="n">
-        <v>18.39619501334948</v>
+        <v>18.31478895123396</v>
       </c>
       <c r="O6" t="n">
-        <v>4.289078573930476</v>
+        <v>4.279578127717026</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0889006574184</v>
+        <v>385.0281841051076</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21579,28 +21779,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.904953947820547</v>
+        <v>-1.901214687367424</v>
       </c>
       <c r="J7" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="K7" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9310008543259608</v>
+        <v>0.9318110915988544</v>
       </c>
       <c r="M7" t="n">
-        <v>2.819652280414239</v>
+        <v>2.814727387497191</v>
       </c>
       <c r="N7" t="n">
-        <v>15.87269134261775</v>
+        <v>15.75992935053394</v>
       </c>
       <c r="O7" t="n">
-        <v>3.984054635998074</v>
+        <v>3.969877750074168</v>
       </c>
       <c r="P7" t="n">
-        <v>381.3277578661628</v>
+        <v>381.2886543561463</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21638,7 +21838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H506"/>
+  <dimension ref="A1:H511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42881,6 +43081,216 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-41.153562787866065,176.02771975569303</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-41.15392462612766,176.02695541362627</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-41.15423976583185,176.0261604601735</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-41.15454353244256,176.02535805207302</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-41.154800761113286,176.02452513924754</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-41.15509533083682,176.0237167041701</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:54:16+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-41.153565610686215,176.02772160610462</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-41.1539277715654,176.026957475503</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-41.15423774951901,176.0261591384664</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-41.15454958140101,176.02536201716734</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-41.154805035725694,176.0245279412239</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-41.15509533083682,176.0237167041701</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-41.15357964413438,176.0277308052963</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-41.15393261070031,176.02696064762148</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-41.154239362569285,176.02616019583206</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-41.15455006531768,176.0253623343749</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-41.15480834250125,176.02453010879083</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-41.15509799239687,176.02371844878428</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-41.15357545023042,176.02772805611215</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-41.15392970721939,176.02695874435034</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-41.15423710429891,176.02615871552015</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-41.154548855526,176.02536154135598</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-41.154806164868575,176.02452868136868</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-41.15509799239687,176.02371844878428</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-41.153574643710414,176.02772752742294</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-41.153930675046354,176.02695937877405</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-41.154236459078795,176.0261582925739</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-41.15454748442876,176.0253606426012</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-41.1548039065828,176.02452720107917</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-41.15509291123676,176.02371511815733</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H511"/>
+  <dimension ref="A1:H514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15762,6 +15762,96 @@
         <v>332.13</v>
       </c>
       <c r="H511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:59:43+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>320.72</v>
+      </c>
+      <c r="C512" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="D512" t="n">
+        <v>331.67</v>
+      </c>
+      <c r="E512" t="n">
+        <v>335.29</v>
+      </c>
+      <c r="F512" t="n">
+        <v>332.73</v>
+      </c>
+      <c r="G512" t="n">
+        <v>331.64</v>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>320.38</v>
+      </c>
+      <c r="C513" t="n">
+        <v>328.82</v>
+      </c>
+      <c r="D513" t="n">
+        <v>331.91</v>
+      </c>
+      <c r="E513" t="n">
+        <v>335.31</v>
+      </c>
+      <c r="F513" t="n">
+        <v>332.49</v>
+      </c>
+      <c r="G513" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:54:10+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>321.47</v>
+      </c>
+      <c r="C514" t="n">
+        <v>329.42</v>
+      </c>
+      <c r="D514" t="n">
+        <v>332.46</v>
+      </c>
+      <c r="E514" t="n">
+        <v>335.21</v>
+      </c>
+      <c r="F514" t="n">
+        <v>332.06</v>
+      </c>
+      <c r="G514" t="n">
+        <v>331.12</v>
+      </c>
+      <c r="H514" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15778,7 +15868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B544"/>
+  <dimension ref="A1:B547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21221,6 +21311,36 @@
       </c>
       <c r="B544" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-05-26 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -21389,28 +21509,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.581178051378834</v>
+        <v>-2.57741082006339</v>
       </c>
       <c r="J2" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K2" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8928830388774621</v>
+        <v>0.8935413035951624</v>
       </c>
       <c r="M2" t="n">
-        <v>5.342466970941737</v>
+        <v>5.334079458840796</v>
       </c>
       <c r="N2" t="n">
-        <v>47.5609103671654</v>
+        <v>47.3581397343314</v>
       </c>
       <c r="O2" t="n">
-        <v>6.896441862813417</v>
+        <v>6.881725055124726</v>
       </c>
       <c r="P2" t="n">
-        <v>386.4727672370725</v>
+        <v>386.433221519054</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21467,28 +21587,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.380283144312241</v>
+        <v>-2.371504909690358</v>
       </c>
       <c r="J3" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="L3" t="n">
-        <v>0.912206003152494</v>
+        <v>0.9115340869442243</v>
       </c>
       <c r="M3" t="n">
-        <v>4.514850240789157</v>
+        <v>4.539884824035653</v>
       </c>
       <c r="N3" t="n">
-        <v>32.44738478989174</v>
+        <v>32.65968073696742</v>
       </c>
       <c r="O3" t="n">
-        <v>5.696260597083997</v>
+        <v>5.714864892275882</v>
       </c>
       <c r="P3" t="n">
-        <v>384.5527632317396</v>
+        <v>384.4606223384617</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21545,28 +21665,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.196794977973306</v>
+        <v>-2.191948187673286</v>
       </c>
       <c r="J4" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K4" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9191791138529414</v>
+        <v>0.9193350715425107</v>
       </c>
       <c r="M4" t="n">
-        <v>3.713990667848423</v>
+        <v>3.72198188434237</v>
       </c>
       <c r="N4" t="n">
-        <v>25.24951708105859</v>
+        <v>25.22506660407858</v>
       </c>
       <c r="O4" t="n">
-        <v>5.024889758100031</v>
+        <v>5.022456232171524</v>
       </c>
       <c r="P4" t="n">
-        <v>386.2959393006879</v>
+        <v>386.2450622575441</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21623,28 +21743,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.134960832914614</v>
+        <v>-2.129692164230882</v>
       </c>
       <c r="J5" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K5" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9338491609014723</v>
+        <v>0.9337828378483414</v>
       </c>
       <c r="M5" t="n">
-        <v>3.152992926131599</v>
+        <v>3.162432575505531</v>
       </c>
       <c r="N5" t="n">
-        <v>19.21272693887974</v>
+        <v>19.24505564129835</v>
       </c>
       <c r="O5" t="n">
-        <v>4.383232476024941</v>
+        <v>4.386918695542276</v>
       </c>
       <c r="P5" t="n">
-        <v>387.4915636002148</v>
+        <v>387.4362621554013</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21701,28 +21821,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.105202404413347</v>
+        <v>-2.101127298752532</v>
       </c>
       <c r="J6" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9342591969266896</v>
+        <v>0.9344386730673052</v>
       </c>
       <c r="M6" t="n">
-        <v>3.171461873754909</v>
+        <v>3.17881975026157</v>
       </c>
       <c r="N6" t="n">
-        <v>18.31478895123396</v>
+        <v>18.29258083115342</v>
       </c>
       <c r="O6" t="n">
-        <v>4.279578127717026</v>
+        <v>4.276982678378932</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0281841051076</v>
+        <v>384.9849935377626</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21779,28 +21899,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.901214687367424</v>
+        <v>-1.900134719322214</v>
       </c>
       <c r="J7" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K7" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9318110915988544</v>
+        <v>0.9324352845548092</v>
       </c>
       <c r="M7" t="n">
-        <v>2.814727387497191</v>
+        <v>2.804761853561986</v>
       </c>
       <c r="N7" t="n">
-        <v>15.75992935053394</v>
+        <v>15.67388147422928</v>
       </c>
       <c r="O7" t="n">
-        <v>3.969877750074168</v>
+        <v>3.959025318715363</v>
       </c>
       <c r="P7" t="n">
-        <v>381.2886543561463</v>
+        <v>381.2773234315349</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21838,7 +21958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H511"/>
+  <dimension ref="A1:H514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43291,6 +43411,132 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:59:43+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-41.1535715789344,176.02772551840405</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-41.15392462612766,176.02695541362627</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-41.15423161992786,176.02615512047737</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-41.15454667790096,176.02536011392198</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-41.15481189123596,176.02453243496043</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-41.15508895922325,176.02371252767006</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-41.15356883676633,176.027723720861</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-41.1539227711259,176.02695419764774</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-41.15423355558825,176.02615638931593</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-41.154546839206525,176.0253602196578</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-41.1548099555625,176.02453116614063</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-41.15508605570307,176.02371062445516</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:54:10+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-41.15357762783441,176.0277294835731</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-41.15392761026091,176.02695736976574</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-41.15423799147656,176.02615929707125</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-41.15454603267874,176.02535969097858</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-41.15480648748082,176.02452889283862</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-41.15508476524964,176.0237097785819</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
